--- a/genai_activity_guidance_table.xlsx
+++ b/genai_activity_guidance_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gla-my.sharepoint.com/personal/helena_paterson_glasgow_ac_uk/Documents/Documents/assessmentai/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2068" documentId="8_{29B8CF80-18B1-42DD-994F-A015760602C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C23C29A-72D9-4200-A647-A84D754E677A}"/>
+  <xr:revisionPtr revIDLastSave="2070" documentId="8_{29B8CF80-18B1-42DD-994F-A015760602C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{775D90E5-3864-4EC8-AF54-16D997A511CF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AI statement master table" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4389" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4389" uniqueCount="492">
   <si>
     <t>Main Skills Category</t>
   </si>
@@ -1425,9 +1425,6 @@
     <t>Presentation, Proposal,</t>
   </si>
   <si>
-    <t>none; consider if needed to tease appart 'finding' and 'selecting', compare with: Identifying Gaps and Critical Evaluation</t>
-  </si>
-  <si>
     <t>Formulating clear research questions and hypotheses based on literature consultation. The gold standard is to identify gaps in knowledge and propose testable ideas through critical analysis of literature. Support is available through research skills training, peer support, and supervisor feedback.</t>
   </si>
   <si>
@@ -1452,36 +1449,21 @@
     <t>Condensing a longer report, project, or dissertation into a concise summary highlighting gaps in knowledge, objectives, methods, results, and conclusions. The gold standard is for students to synthesise their own key points, capture the significance of their work accurately, and present a balanced overview without omitting critical information. Support is available through writing workshops, study guides, and staff or peer feedback.</t>
   </si>
   <si>
-    <t>Column B: added "gaps in knowledge" ; column C, added:"GenAI can also be helpful for suggesting improvements to writing efficiency, to fit into specifed word limits."</t>
-  </si>
-  <si>
     <t>Use GenAI to review example abstracts or summary structures, or to suggest different ways of ordering key points, helping you check clarity and balance. You can also ask GenAI to highlight jargon or overly complex sentences so you can refine your own wording. GenAI can also be helpful for suggesting improvements to writing efficiency, to fit into specified word limits.  Always ensure the abstract or summary is written by you, based on your actual work, and reflects your own interpretation of what is most important.</t>
   </si>
   <si>
     <t>Use GenAI as a computer language assistant without letting it replace your understanding. You can ask GenAI to troubleshoot coding errors, clarify syntax, or explain unfamiliar functions step by step. You may also use it to walk through logic flows, provide worked examples, or suggest debugging strategies — but you remain in charge of writing, adapting, testing and annotating your code for reproducibility. Good practice means using GenAI as a tutor to support problem-solving and deepen your coding knowledge and citing the tools that you use in your scripts. Although you can use GenAI to assess whether you have provided sufficiently clear annotations to ensure repeatability, annotations should be in your own voice.</t>
   </si>
   <si>
-    <t>Column C- maybe not quite the right worded but added:"Although you can use GenAI to assess whether you have provided sufficiently clear annotations to ensure repeatability, annotations should be in your own voice."</t>
-  </si>
-  <si>
-    <t>Was thinking of adding something like this to column C but not sure whether it fits: "You should write descriptive captions yourself because GenAI will not be as good as intepreting patterns demonstrated."</t>
-  </si>
-  <si>
     <t>Use GenAI to learn wrangling techniques and syntax — for example, asking for explanations of tidyverse functions in R, help writing,  debugging or cleaning scripts, or advice on how to structure a reproducible workflow. GenAI can also help you think through edge cases (e.g. how to handle outliers or missing data) or draft documentation of your cleaning steps. Good practice means you make and justify the actual decisions about your data, run and verify the code yourself, and keep a clear audit trail of changes. Never upload unpublished, identifiable, or sensitive data into GenAI tools — use simulated or dummy data when asking for coding help instead.</t>
   </si>
   <si>
-    <t>Data-to-visual transformation assignment, Raw data to analysis report,Critique of published visualisations, Visual storytelling task with dataset</t>
-  </si>
-  <si>
     <t>Keep ownership of the content, using GenAI only to refine or extend your ideas and support the production process. Set clear direction, give specific prompts, critically review outputs, and make final edits so that the final product reflects your own voice. GenAI can suggest visual cues, editing tips, or draft script outlines, and help check clarity and accessibility — but you must ensure all outputs comply with regulatory requirements (e.g. copyright).</t>
   </si>
   <si>
     <t>Column C: added "(e.g. copyright)"</t>
   </si>
   <si>
-    <t>Avoid relying on GenAI instead of taking real practice opportunities provided through teaching and peer support. This would limit your ability to rehearse responses to genuine audience questions and weakens the communication skills needed for academic and professional growth. Improving structure and delivery based on feedback from teachers or peers is an important part of the learning process.Using GenAI to draft or memorise large parts of a script prevents you from developing subject expertise, learning how to communicate your discipline effectively, reframing knowledge for different audiences, and building confidence in explaining ideas in your own words.</t>
-  </si>
-  <si>
     <t>consider shorter name--not shorter but could change to Drafting and Rehearsing Oral Presentations; IBM- I'm not sure I understand this part: "The focus is on oral communication rather than the design of accompanying material such as slides or a poster." This seemed to also be about structuring the content.  To column D, added:" Improving structure and delivery based on feedback from teachers or peers is an important part of the learning process."</t>
   </si>
   <si>
@@ -1491,9 +1473,6 @@
     <t>Use GenAI to brainstorm outlines, generate alternative structures, or test phrasing for clarity and persuasiveness. You can also ask GenAI to check readability or highlight jargon, but final decisions must reflect your own knowledge and project specifics.  Good practice means developing and pitching a convincing idea for a future study, motivated by your own creativity but set into the background of existing research.</t>
   </si>
   <si>
-    <t>to columen B, added: "gaps in knowledge", "experimental design".  To column C added:"Good practice means developing and pitching a convincing idea for a future study, motivated by your own creativity but set into the background of existing research."  To column D, added: "design"</t>
-  </si>
-  <si>
     <t>First interpret your results yourself, then use available resources to improve clarity and depth, which may include GenAI. Use GenAI to practise communicating your findings by generating alternative phrasings, asking it to highlight unclear sections, or drafting practice questions that test your reasoning. You can also use GenAI to simulate counter-arguments or alternative explanations, which you must then address in your own words. These uses can help refine your ability to express your interpretation clearly and critically.  Good practice means critically analysing your results, explaining what they mean, while considering possible limitations.</t>
   </si>
   <si>
@@ -1509,12 +1488,6 @@
     <t>Maybe best to avoid specific jargon: HARKing, p-hacking,</t>
   </si>
   <si>
-    <t>Column B: Does this have to be specfied? "to support a spoken or performed presentation" arguably a poster could stand alone?  Or, do we need a separate poster section because that is arguably more susceptible to AI-overuse than oral presentation?</t>
-  </si>
-  <si>
-    <t>To column B, added "Include digital object identifier (doi) codes whenever possible, to enable direct linking to the source."  Column D, added: "For example, it can make up doi codes."   We could add the text I had in the case study: "GenAI generated reference lists can take more time to check for accuracy than searches such as Web of Science and Google Scholar because hallucinations can take multiple forms: 1) completely invented reference; 2) invented digital object identifier even if the rest of the reference is correct; 3) some details of the citation correct but others invented (e.g. wrong journal); 4) improper formatting of citations or bibliography."</t>
-  </si>
-  <si>
     <t>Poster Presentations</t>
   </si>
   <si>
@@ -1536,33 +1509,18 @@
     <t>Editing and Proofreading</t>
   </si>
   <si>
-    <t>Use GenAI as a support tool to provide feedback on your own draft, such as highlighting errors, outlining shortcomings and suggesting alternatives. Assistive technology tools such as grammarly and other grammar and spelling software may be useful. Critically review suggestions and decide which changes to implement to help maintain your own voice, because the work is a reflection of you. Transparently acknowledge the use of GenAI for this purpose in your work and keep a record of your interactions with the tool.</t>
-  </si>
-  <si>
-    <t>Check overlap with Finalisation and Submission Preparation; Removed structuring from name; column C, added: "Assistive technology tools such as grammarly and other grammar and spelling software may be useful."</t>
-  </si>
-  <si>
     <t>Translation</t>
   </si>
   <si>
     <t>Data Processing</t>
   </si>
   <si>
-    <t>new section-BM made minor corrections; check against: Technology-assisted data collection and transformation. In column D, I wasn't sure what "silent" meant in this context.  I'm also not sure I understand this clause: rather than as one input to your own judgement. BM added suggested skills category and asessment but should be checked; changed title to Data Processing</t>
-  </si>
-  <si>
-    <t>GenAI offers sophisticated enhancement of translation software, and this is an expanding field that has significant future implications for communication across language barriers. Use GenAI-powered translation software to assit with translation of original work that you produce in another language to English (unless the testing of English Language is an ILO). Note that the nuance of an intended communication is likely to be lost or changed during any AI-assisted translation process so output should be carefully edited and refined. You can use it to help you to understand where you are making common mistakes in your use of English, to help to improve your writing in the future.  Good practice means using GenAI to help you to express your ideas more clearly but it should not be used to replace your own writing.</t>
-  </si>
-  <si>
     <t>Bm added; please check</t>
   </si>
   <si>
     <t>Online formative quizzes with rationale, Confidence rating alongside answers, Self-generated MCQs with explanations, upload source material (with permission) to institution-supported AI-tool and simulate interactive revision</t>
   </si>
   <si>
-    <t>review name for conciseness and accuracy; BM: this isn't quite the self-assessment I was thinking about (i.e.revising for exam).;  column C, added: "and improving recall'  based on Carolyn's comment; added direct assm: AI revision</t>
-  </si>
-  <si>
     <t>Translation decision log, Error detection exercise</t>
   </si>
   <si>
@@ -1584,9 +1542,6 @@
     <t>BM added -please check</t>
   </si>
   <si>
-    <t>Using GenAI for translation without knowing enough English to intepret meanings risks mispresentation of your ideas, or altering credit given via in-text citations. Translation should not be used as a replacement of learning to clearly communicate in English.  Failing to critically check outputs also risks miscommunicating field-specific terminology or using inappropriate terminology for your discipline. Over-reliance on GenAI limits your opportunity for practicing and improving communication in English, as well as confidence in the use of scientific and technical English.</t>
-  </si>
-  <si>
     <t>Reflection, Problem centred</t>
   </si>
   <si>
@@ -1683,7 +1638,64 @@
     <t>Proposal, Research project, Groupwork, Essay or similar, Data analysis report, Practical skills, Reflection</t>
   </si>
   <si>
-    <t>Translating written work from another language into English.  Students who are are not Enghlish first language speakers will often need to translate their thoughts from their primary language to English. The gold standard is to write the text in English from the start but where this creates challenges that compromise demonstration of learning, translation might be necessary. Support is available through English as a second language support, and feedback from staff or peers.</t>
+    <t>Column B: added "gaps in knowledge" ; column C, added: "GenAI can also be helpful for suggesting improvements to writing efficiency, to fit into specified word limits."</t>
+  </si>
+  <si>
+    <t>Column C- maybe not quite the right worded but added: "Although you can use GenAI to assess whether you have provided sufficiently clear annotations to ensure repeatability, annotations should be in your own voice."</t>
+  </si>
+  <si>
+    <t>Was thinking of adding something like this to column C but not sure whether it fits: "You should write descriptive captions yourself because GenAI will not be as good as interpreting patterns demonstrated."</t>
+  </si>
+  <si>
+    <t>Data-to-visual transformation assignment, Raw data to analysis report, Critique of published visualisations, Visual storytelling task with dataset</t>
+  </si>
+  <si>
+    <t>new section-BM made minor corrections; check against: Technology-assisted data collection and transformation. In column D, I wasn't sure what "silent" meant in this context.  I'm also not sure I understand this clause: rather than as one input to your own judgement. BM added suggested skills category and assessment but should be checked; changed title to Data Processing</t>
+  </si>
+  <si>
+    <t>Critical literature review, Gap identification and research need report, SWOT (Strength, Weakness, Opportunity, Threat) analysis of existing studies</t>
+  </si>
+  <si>
+    <t>none; consider if needed to tease apart 'finding' and 'selecting', compare with: Identifying Gaps and Critical Evaluation</t>
+  </si>
+  <si>
+    <t>Avoid relying on GenAI instead of taking real practice opportunities provided through teaching and peer support. This would limit your ability to rehearse responses to genuine audience questions and weakens the communication skills needed for academic and professional growth. Improving structure and delivery based on feedback from teachers or peers is an important part of the learning process. Using GenAI to draft or memorise large parts of a script prevents you from developing subject expertise, learning how to communicate your discipline effectively, reframing knowledge for different audiences, and building confidence in explaining ideas in your own words.</t>
+  </si>
+  <si>
+    <t>to column B, added: "gaps in knowledge", "experimental design".  To column C added: "Good practice means developing and pitching a convincing idea for a future study, motivated by your own creativity but set into the background of existing research."  To column D, added: "design"</t>
+  </si>
+  <si>
+    <t>review name for conciseness and accuracy; BM: this isn't quite the self-assessment I was thinking about (i.e. Revising for exam).;  column C, added: "and improving recall'  based on Carolyn's comment; added direct assm: AI revision</t>
+  </si>
+  <si>
+    <t>Use GenAI as a support tool to provide feedback on your own draft, such as highlighting errors, outlining shortcomings and suggesting alternatives. Assistive technology tools such as Grammarly and other grammar and spelling software may be useful. Critically review suggestions and decide which changes to implement to help maintain your own voice, because the work is a reflection of you. Transparently acknowledge the use of GenAI for this purpose in your work and keep a record of your interactions with the tool.</t>
+  </si>
+  <si>
+    <t>Check overlap with Finalisation and Submission Preparation; Removed structuring from name; column C, added: "Assistive technology tools such as Grammarly and other grammar and spelling software may be useful."</t>
+  </si>
+  <si>
+    <t>Using GenAI to create presentation content on your behalf places you at risk of suspected misconduct by outsourcing ownership of your ideas. Failing to effectively instruct or critically check GenAI outputs may introduce errors or misleading visuals. Over-reliance on GenAI to design presentations limits your opportunity to practise structuring visual aids for presentations and developing important digital skills for academic and professional growth.</t>
+  </si>
+  <si>
+    <t>Column B: Does this have to be specified? "to support a spoken or performed presentation" arguably a poster could stand alone?  Or, do we need a separate poster section because that is arguably more susceptible to AI-overuse than oral presentation?</t>
+  </si>
+  <si>
+    <t>Translating written work from another language into English.  Students who are  not English first language speakers will often need to translate their thoughts from their primary language to English. The gold standard is to write the text in English from the start but where this creates challenges that compromise demonstration of learning, translation might be necessary. Support is available through English as a second language support, and feedback from staff or peers.</t>
+  </si>
+  <si>
+    <t>GenAI offers sophisticated enhancement of translation software, and this is an expanding field that has significant future implications for communication across language barriers. Use GenAI-powered translation software to assist with translation of original work that you produce in another language to English (unless the testing of English Language is an ILO). Note that the nuance of an intended communication is likely to be lost or changed during any AI-assisted translation process so output should be carefully edited and refined. You can use it to help you to understand where you are making common mistakes in your use of English, to help to improve your writing in the future.  Good practice means using GenAI to help you to express your ideas more clearly but it should not be used to replace your own writing.</t>
+  </si>
+  <si>
+    <t>Using GenAI for translation without knowing enough English to interpret meanings risks mispresentation of your ideas, or altering credit given via in-text citations. Translation should not be used as a replacement of learning to clearly communicate in English.  Failing to critically check outputs also risks miscommunicating field-specific terminology or using inappropriate terminology for your discipline. Over-reliance on GenAI limits your opportunity for practicing and improving communication in English, as well as confidence in the use of scientific and technical English.</t>
+  </si>
+  <si>
+    <t>Tracking bibliographic details for every source you consult and format citations correctly (e.g. APA, Harvard). Keep notes on which information comes from which source, use reference management tools such as EndNote, Mendeley or Zotero, and check formatting. Always ensure the correct source is credited for each idea in your work. Include digital object identifier (Doi) codes whenever possible, to enable direct linking to the source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using GenAI to insert citations or build a reference list can lead to fabricated sources and mismatched attributions, creating inaccuracies that may amount to misconduct. For example, it can make up Doi codes or link to the wrong source. Relying on GenAI too heavily can also mean you fail to learn the purpose of citations, or your field’s referencing style to substantiate arguments, leaving you unprepared for larger projects such as a dissertation.  </t>
+  </si>
+  <si>
+    <t>To column B, added "Include digital object identifier (doi) codes whenever possible, to enable direct linking to the source."  Column D, added: "For example, it can make up Doi codes."   We could add the text I had in the case study: "GenAI generated reference lists can take more time to check for accuracy than searches such as Web of Science and Google Scholar because hallucinations can take multiple forms: 1) completely invented reference; 2) invented digital object identifier even if the rest of the reference is correct; 3) some details of the citation correct but others invented (e.g. wrong journal); 4) improper formatting of citations or bibliography."</t>
   </si>
 </sst>
 </file>
@@ -4031,10 +4043,10 @@
         <v>0</v>
       </c>
       <c r="F1" s="31" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="G1" s="26" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="H1" s="40" t="s">
         <v>370</v>
@@ -4048,19 +4060,19 @@
         <v>39</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="D2" s="8" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="G2" s="14" t="s">
         <v>320</v>
@@ -4069,7 +4081,7 @@
         <v>358</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>410</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="172.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4089,7 +4101,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="61" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>306</v>
@@ -4109,7 +4121,7 @@
         <v>141</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>304</v>
@@ -4118,7 +4130,7 @@
         <v>64</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="G4" s="14" t="s">
         <v>332</v>
@@ -4127,7 +4139,7 @@
         <v>356</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>413</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="82.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4147,7 +4159,7 @@
         <v>29</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>316</v>
@@ -4176,7 +4188,7 @@
         <v>29</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="G6" s="15" t="s">
         <v>324</v>
@@ -4205,7 +4217,7 @@
         <v>64</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>331</v>
@@ -4214,36 +4226,36 @@
         <v>375</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>414</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="213" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>391</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="D8" s="62" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>64</v>
       </c>
       <c r="F8" s="32" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>416</v>
+        <v>475</v>
       </c>
       <c r="H8" s="41" t="s">
         <v>375</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>442</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="112.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4263,7 +4275,7 @@
         <v>29</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="G9" s="56" t="s">
         <v>326</v>
@@ -4272,7 +4284,7 @@
         <v>362</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="108" customHeight="1" x14ac:dyDescent="0.3">
@@ -4286,13 +4298,13 @@
         <v>396</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F10" s="32" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="G10" s="14" t="s">
         <v>315</v>
@@ -4309,7 +4321,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>165</v>
@@ -4321,7 +4333,7 @@
         <v>336</v>
       </c>
       <c r="F11" s="32" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>311</v>
@@ -4330,7 +4342,7 @@
         <v>359</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="114" customHeight="1" x14ac:dyDescent="0.3">
@@ -4341,7 +4353,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>101</v>
@@ -4350,7 +4362,7 @@
         <v>12</v>
       </c>
       <c r="F12" s="32" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="G12" s="14" t="s">
         <v>309</v>
@@ -4359,7 +4371,7 @@
         <v>355</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="136.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
@@ -4379,7 +4391,7 @@
         <v>29</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>317</v>
@@ -4396,10 +4408,10 @@
         <v>35</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>406</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>407</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>112</v>
@@ -4408,7 +4420,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="32" t="s">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="G14" s="14" t="s">
         <v>318</v>
@@ -4417,7 +4429,7 @@
         <v>378</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="96.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4437,10 +4449,10 @@
         <v>336</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>312</v>
+        <v>477</v>
       </c>
       <c r="H15" s="41" t="s">
         <v>372</v>
@@ -4460,13 +4472,13 @@
         <v>387</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>7</v>
       </c>
       <c r="F16" s="32" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="G16" s="14" t="s">
         <v>307</v>
@@ -4475,7 +4487,7 @@
         <v>354</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>401</v>
+        <v>478</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="114" customHeight="1" x14ac:dyDescent="0.3">
@@ -4483,19 +4495,19 @@
         <v>10</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>389</v>
+        <v>489</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>100</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>392</v>
+        <v>490</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>7</v>
       </c>
       <c r="F17" s="32" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="G17" s="14" t="s">
         <v>308</v>
@@ -4504,7 +4516,7 @@
         <v>354</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>430</v>
+        <v>491</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="124.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4515,7 +4527,7 @@
         <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>133</v>
@@ -4533,12 +4545,12 @@
         <v>371</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="97.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="37" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>170</v>
@@ -4553,7 +4565,7 @@
         <v>336</v>
       </c>
       <c r="F19" s="32" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="G19" s="14" t="s">
         <v>313</v>
@@ -4567,7 +4579,7 @@
     </row>
     <row r="20" spans="1:9" ht="160.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>116</v>
@@ -4576,7 +4588,7 @@
         <v>117</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>419</v>
+        <v>479</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>45</v>
@@ -4591,7 +4603,7 @@
         <v>357</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="117" customHeight="1" x14ac:dyDescent="0.3">
@@ -4611,7 +4623,7 @@
         <v>336</v>
       </c>
       <c r="F21" s="32" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="G21" s="15" t="s">
         <v>334</v>
@@ -4640,7 +4652,7 @@
         <v>336</v>
       </c>
       <c r="F22" s="32" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="G22" s="14" t="s">
         <v>335</v>
@@ -4669,7 +4681,7 @@
         <v>12</v>
       </c>
       <c r="F23" s="32" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="G23" s="14" t="s">
         <v>321</v>
@@ -4686,13 +4698,13 @@
         <v>24</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>12</v>
@@ -4707,7 +4719,7 @@
         <v>357</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>423</v>
+        <v>480</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="142.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -4718,16 +4730,16 @@
         <v>128</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>336</v>
       </c>
       <c r="F25" s="32" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="G25" s="14" t="s">
         <v>327</v>
@@ -4736,7 +4748,7 @@
         <v>376</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="103.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4765,7 +4777,7 @@
         <v>357</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4785,7 +4797,7 @@
         <v>45</v>
       </c>
       <c r="F27" s="32" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="G27" s="14" t="s">
         <v>329</v>
@@ -4803,7 +4815,7 @@
         <v>155</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>157</v>
@@ -4812,16 +4824,16 @@
         <v>4</v>
       </c>
       <c r="F28" s="32" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="H28" s="41" t="s">
         <v>373</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>446</v>
+        <v>481</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="133.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
@@ -4829,7 +4841,7 @@
         <v>66</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>148</v>
@@ -4841,7 +4853,7 @@
         <v>64</v>
       </c>
       <c r="F29" s="32" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>333</v>
@@ -4853,13 +4865,13 @@
     </row>
     <row r="30" spans="1:9" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="37" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>438</v>
+        <v>482</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>102</v>
@@ -4868,7 +4880,7 @@
         <v>12</v>
       </c>
       <c r="F30" s="32" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="G30" s="14" t="s">
         <v>310</v>
@@ -4877,7 +4889,7 @@
         <v>374</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>439</v>
+        <v>483</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="133.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -4891,7 +4903,7 @@
         <v>138</v>
       </c>
       <c r="D31" s="55" t="s">
-        <v>139</v>
+        <v>484</v>
       </c>
       <c r="E31" s="21" t="s">
         <v>45</v>
@@ -4906,50 +4918,50 @@
         <v>358</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>429</v>
+        <v>485</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="193.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="17" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="B32" s="18" t="s">
+        <v>486</v>
+      </c>
+      <c r="C32" s="59" t="s">
         <v>487</v>
       </c>
-      <c r="C32" s="59" t="s">
-        <v>443</v>
-      </c>
       <c r="D32" s="19" t="s">
-        <v>454</v>
+        <v>488</v>
       </c>
       <c r="E32" s="21" t="s">
         <v>45</v>
       </c>
       <c r="F32" s="32" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="H32" s="42" t="s">
         <v>355</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="153" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="17" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="E33" s="21" t="s">
         <v>45</v>
@@ -4958,42 +4970,42 @@
         <v>236</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="H33" s="42" t="s">
         <v>358</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="166.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="17" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="B34" s="58" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="C34" s="58" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="D34" s="58" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="E34" s="21" t="s">
         <v>4</v>
       </c>
       <c r="F34" s="60" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="H34" s="42" t="s">
         <v>378</v>
       </c>
       <c r="I34" s="57" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
